--- a/data/trans_dic/P15-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P15-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,09; 13,7</t>
+          <t>8,29; 14,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,36; 16,71</t>
+          <t>10,23; 16,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,68; 13,77</t>
+          <t>7,59; 13,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 10,49</t>
+          <t>2,06; 9,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,19; 7,46</t>
+          <t>3,16; 7,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,03; 10,15</t>
+          <t>5,04; 10,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,9; 7,11</t>
+          <t>2,88; 7,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,11; 11,3</t>
+          <t>3,22; 11,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,27; 9,74</t>
+          <t>6,27; 9,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,39; 12,61</t>
+          <t>8,46; 12,27</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,05; 9,74</t>
+          <t>5,88; 9,62</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 8,92</t>
+          <t>3,33; 8,81</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,76; 10,89</t>
+          <t>6,76; 10,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,57; 14,58</t>
+          <t>9,53; 14,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,52; 10,95</t>
+          <t>6,55; 11,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,77; 10,4</t>
+          <t>3,86; 10,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 7,86</t>
+          <t>3,95; 7,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,75; 8,9</t>
+          <t>4,76; 8,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,76</t>
+          <t>2,7; 5,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,81</t>
+          <t>1,45; 4,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,07; 8,87</t>
+          <t>5,99; 8,87</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,86; 11,08</t>
+          <t>7,86; 11,22</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,04; 7,84</t>
+          <t>5,15; 7,91</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,07; 6,65</t>
+          <t>2,88; 6,5</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,22; 9,45</t>
+          <t>5,31; 9,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,3; 10,81</t>
+          <t>6,19; 10,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 7,5</t>
+          <t>3,69; 7,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,02; 9,43</t>
+          <t>4,87; 9,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,41</t>
+          <t>1,81; 4,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 5,84</t>
+          <t>2,84; 5,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,71</t>
+          <t>2,5; 5,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 6,82</t>
+          <t>3,83; 7,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 6,24</t>
+          <t>3,87; 6,3</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,97; 7,6</t>
+          <t>4,99; 7,7</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,48; 5,88</t>
+          <t>3,46; 5,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,64; 7,41</t>
+          <t>4,65; 7,44</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 10,93</t>
+          <t>5,81; 10,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,41; 8,49</t>
+          <t>4,33; 8,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,96; 6,38</t>
+          <t>2,84; 6,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 8,58</t>
+          <t>2,4; 8,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 5,86</t>
+          <t>2,37; 6,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,13; 8,12</t>
+          <t>3,96; 8,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 5,65</t>
+          <t>2,4; 5,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,0; 5,44</t>
+          <t>2,99; 5,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,51; 7,53</t>
+          <t>4,41; 7,55</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,39</t>
+          <t>4,58; 7,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 5,36</t>
+          <t>3,07; 5,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,12; 6,49</t>
+          <t>2,83; 6,45</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,0; 7,47</t>
+          <t>3,01; 7,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,72; 5,12</t>
+          <t>1,7; 5,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,83</t>
+          <t>1,62; 4,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 7,33</t>
+          <t>3,64; 7,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,69; 6,72</t>
+          <t>2,7; 6,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,65; 12,42</t>
+          <t>6,56; 12,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,07; 8,98</t>
+          <t>3,98; 8,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,02; 8,22</t>
+          <t>4,92; 8,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,24; 6,38</t>
+          <t>3,27; 6,39</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,58; 7,99</t>
+          <t>4,64; 8,03</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,29</t>
+          <t>3,26; 6,06</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,67; 7,11</t>
+          <t>4,58; 7,17</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,03; 6,32</t>
+          <t>2,13; 6,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,05; 8,68</t>
+          <t>3,24; 8,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,63</t>
+          <t>1,67; 5,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,8; 6,31</t>
+          <t>3,0; 6,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,9; 10,52</t>
+          <t>5,1; 10,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,69; 10,19</t>
+          <t>4,69; 9,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,19; 10,71</t>
+          <t>5,35; 10,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,31; 8,9</t>
+          <t>2,26; 8,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,76</t>
+          <t>4,05; 7,49</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,61; 8,53</t>
+          <t>4,72; 8,75</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,13; 7,69</t>
+          <t>4,09; 7,89</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,67; 6,95</t>
+          <t>2,63; 6,77</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,19; 7,95</t>
+          <t>2,15; 7,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,39; 13,03</t>
+          <t>5,79; 12,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,49; 9,13</t>
+          <t>3,53; 9,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,21; 9,84</t>
+          <t>5,42; 10,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,07; 14,16</t>
+          <t>6,82; 13,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,54; 17,77</t>
+          <t>10,62; 17,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,13; 14,06</t>
+          <t>7,24; 14,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,35; 14,75</t>
+          <t>10,18; 14,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,74; 10,48</t>
+          <t>5,9; 11,0</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,73; 14,74</t>
+          <t>9,4; 14,56</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,45; 11,12</t>
+          <t>6,38; 11,2</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,87; 11,98</t>
+          <t>8,8; 12,13</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,51; 8,33</t>
+          <t>6,48; 8,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,42; 9,43</t>
+          <t>7,45; 9,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,08; 6,7</t>
+          <t>5,14; 6,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,51; 6,87</t>
+          <t>4,44; 6,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,47; 6,11</t>
+          <t>4,5; 6,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,37; 8,16</t>
+          <t>6,47; 8,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,71; 6,2</t>
+          <t>4,62; 6,2</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,85; 6,79</t>
+          <t>4,72; 6,61</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,69; 6,93</t>
+          <t>5,74; 7,01</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7,13; 8,48</t>
+          <t>7,08; 8,47</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,11; 6,22</t>
+          <t>5,12; 6,2</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,98; 6,49</t>
+          <t>4,95; 6,47</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>39992; 67682</t>
+          <t>40959; 69347</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>47035; 75906</t>
+          <t>46444; 75220</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32230; 57768</t>
+          <t>31832; 58065</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8671; 41973</t>
+          <t>8259; 39710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14904; 34854</t>
+          <t>14753; 33030</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21658; 43683</t>
+          <t>21698; 43671</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11476; 28152</t>
+          <t>11402; 27684</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9735; 35376</t>
+          <t>10076; 35485</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>60296; 93694</t>
+          <t>60314; 95123</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74185; 111542</t>
+          <t>74775; 108498</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49317; 79384</t>
+          <t>47899; 78387</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22672; 63586</t>
+          <t>23757; 62839</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49712; 80106</t>
+          <t>49721; 80856</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65754; 100184</t>
+          <t>65461; 100658</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38487; 64643</t>
+          <t>38651; 66531</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15979; 44037</t>
+          <t>16354; 42442</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23868; 49133</t>
+          <t>24721; 48910</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28986; 54332</t>
+          <t>29075; 53470</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14824; 32470</t>
+          <t>15194; 32888</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7188; 24583</t>
+          <t>7392; 24721</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>82579; 120713</t>
+          <t>81466; 120713</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>102016; 143740</t>
+          <t>101933; 145594</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>58215; 90515</t>
+          <t>59466; 91256</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>28750; 62217</t>
+          <t>26894; 60733</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>33333; 60341</t>
+          <t>33912; 60640</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>42941; 73735</t>
+          <t>42177; 74176</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25332; 50149</t>
+          <t>24680; 49191</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26916; 50590</t>
+          <t>26146; 50917</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13011; 30412</t>
+          <t>12453; 30436</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20391; 41545</t>
+          <t>20186; 41820</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16452; 37750</t>
+          <t>16511; 37975</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20271; 37017</t>
+          <t>20796; 39223</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>50683; 82937</t>
+          <t>51447; 83738</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>69247; 105796</t>
+          <t>69513; 107299</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46314; 78260</t>
+          <t>45981; 79762</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>50064; 79950</t>
+          <t>50208; 80219</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30404; 56738</t>
+          <t>30162; 55885</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27114; 52187</t>
+          <t>26618; 51779</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19136; 41237</t>
+          <t>18361; 41487</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20087; 76189</t>
+          <t>21270; 77552</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12515; 30203</t>
+          <t>12237; 31294</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25465; 50033</t>
+          <t>24384; 50008</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15777; 36688</t>
+          <t>15601; 37416</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21355; 38746</t>
+          <t>21295; 38233</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>46638; 77913</t>
+          <t>45633; 78087</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>57234; 90934</t>
+          <t>56420; 93202</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40022; 69400</t>
+          <t>39782; 69104</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>50020; 103880</t>
+          <t>45352; 103219</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11610; 28905</t>
+          <t>11635; 28606</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7368; 21970</t>
+          <t>7295; 22159</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7680; 23077</t>
+          <t>7736; 22754</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19822; 41165</t>
+          <t>20430; 39795</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10883; 27151</t>
+          <t>10916; 27833</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29791; 55634</t>
+          <t>29369; 54863</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20201; 44609</t>
+          <t>19783; 42400</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>27496; 45033</t>
+          <t>26954; 45714</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>25630; 50458</t>
+          <t>25886; 50540</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40198; 70114</t>
+          <t>40697; 70469</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32603; 61299</t>
+          <t>31768; 59058</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>51825; 78914</t>
+          <t>50848; 79556</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5940; 18488</t>
+          <t>6246; 18045</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9437; 26897</t>
+          <t>10047; 26774</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5588; 18822</t>
+          <t>5584; 18651</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10316; 23234</t>
+          <t>11033; 23757</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16814; 36082</t>
+          <t>17504; 36390</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16586; 36084</t>
+          <t>16596; 35243</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19606; 40463</t>
+          <t>20207; 41001</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14079; 54131</t>
+          <t>13775; 54127</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>26904; 49303</t>
+          <t>25715; 47591</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30594; 56626</t>
+          <t>31319; 58089</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29429; 54774</t>
+          <t>29106; 56152</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>26111; 67875</t>
+          <t>25709; 66138</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4606; 16681</t>
+          <t>4512; 16112</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>13468; 32564</t>
+          <t>14463; 32265</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8981; 23453</t>
+          <t>9072; 23244</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14729; 27811</t>
+          <t>15326; 28959</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>23600; 47279</t>
+          <t>22773; 46557</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>40991; 69120</t>
+          <t>41315; 69702</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28519; 56244</t>
+          <t>28991; 57076</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>44061; 62792</t>
+          <t>43360; 62846</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>31189; 56998</t>
+          <t>32069; 59818</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>62128; 94151</t>
+          <t>60035; 93015</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>42364; 73091</t>
+          <t>41906; 73584</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>62867; 84872</t>
+          <t>62330; 85939</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>213412; 272920</t>
+          <t>212290; 275280</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>254257; 323070</t>
+          <t>255444; 320308</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>172348; 227456</t>
+          <t>174325; 228532</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>156189; 237795</t>
+          <t>153650; 236555</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>151081; 206321</t>
+          <t>151993; 204526</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>226504; 290278</t>
+          <t>230061; 294681</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>166967; 219653</t>
+          <t>163810; 219660</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>177727; 248580</t>
+          <t>172841; 242043</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>379017; 461354</t>
+          <t>381713; 466311</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>498305; 592513</t>
+          <t>494687; 591726</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>354579; 431587</t>
+          <t>355480; 430098</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>354667; 462516</t>
+          <t>352614; 461129</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P15-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,29; 14,04</t>
+          <t>8,1; 13,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,23; 16,56</t>
+          <t>10,18; 16,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,59; 13,84</t>
+          <t>7,59; 13,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 9,93</t>
+          <t>2,47; 10,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 7,07</t>
+          <t>3,12; 6,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,04; 10,15</t>
+          <t>5,04; 10,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,88; 7,0</t>
+          <t>2,87; 6,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,22; 11,33</t>
+          <t>3,05; 11,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,27; 9,89</t>
+          <t>6,31; 9,67</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,46; 12,27</t>
+          <t>8,32; 12,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,88; 9,62</t>
+          <t>5,81; 9,69</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,33; 8,81</t>
+          <t>3,3; 8,63</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,76; 10,99</t>
+          <t>6,81; 10,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,53; 14,65</t>
+          <t>9,73; 14,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,55; 11,27</t>
+          <t>6,52; 10,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,86; 10,02</t>
+          <t>4,23; 11,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,95; 7,82</t>
+          <t>4,02; 7,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,76; 8,76</t>
+          <t>4,57; 8,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 5,84</t>
+          <t>2,66; 5,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,83</t>
+          <t>1,7; 4,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,99; 8,87</t>
+          <t>5,83; 8,77</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,86; 11,22</t>
+          <t>7,77; 11,09</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,15; 7,91</t>
+          <t>5,05; 7,81</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,5</t>
+          <t>3,54; 7,1</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,31; 9,49</t>
+          <t>5,23; 9,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,19; 10,88</t>
+          <t>6,21; 10,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,69; 7,35</t>
+          <t>3,7; 7,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,87; 9,49</t>
+          <t>4,46; 8,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,41</t>
+          <t>1,8; 4,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,84; 5,88</t>
+          <t>2,8; 5,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,74</t>
+          <t>2,47; 5,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,83; 7,23</t>
+          <t>3,5; 6,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,87; 6,3</t>
+          <t>3,9; 6,33</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 7,7</t>
+          <t>4,8; 7,58</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,46; 5,99</t>
+          <t>3,46; 5,91</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,44</t>
+          <t>4,42; 6,9</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,27 +1104,27 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5,95%</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
           <t>4,12%</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5,9%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5,95%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,81; 10,76</t>
+          <t>5,78; 10,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,33; 8,42</t>
+          <t>4,32; 8,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,84; 6,42</t>
+          <t>3,02; 6,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,4; 8,74</t>
+          <t>5,9; 10,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 6,07</t>
+          <t>2,27; 5,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,96; 8,12</t>
+          <t>4,07; 7,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,76</t>
+          <t>2,38; 5,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,99; 5,36</t>
+          <t>3,44; 5,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,41; 7,55</t>
+          <t>4,53; 7,64</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,58; 7,57</t>
+          <t>4,63; 7,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,07; 5,34</t>
+          <t>3,09; 5,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 6,45</t>
+          <t>5,0; 7,51</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,01; 7,4</t>
+          <t>3,08; 7,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 5,16</t>
+          <t>1,53; 5,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,76</t>
+          <t>1,54; 4,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,64; 7,09</t>
+          <t>3,63; 7,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 6,89</t>
+          <t>2,69; 6,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,56; 12,25</t>
+          <t>6,63; 12,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,98; 8,53</t>
+          <t>4,17; 9,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,92; 8,34</t>
+          <t>4,93; 7,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,27; 6,39</t>
+          <t>3,36; 6,3</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,64; 8,03</t>
+          <t>4,82; 8,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,26; 6,06</t>
+          <t>3,28; 6,13</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,58; 7,17</t>
+          <t>4,69; 6,97</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,13; 6,17</t>
+          <t>1,9; 6,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,24; 8,64</t>
+          <t>3,44; 9,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,58</t>
+          <t>1,65; 5,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,0; 6,45</t>
+          <t>2,9; 6,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,1; 10,61</t>
+          <t>5,21; 10,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,69; 9,96</t>
+          <t>4,93; 10,31</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,35; 10,85</t>
+          <t>5,33; 11,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,26; 8,9</t>
+          <t>6,48; 10,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,05; 7,49</t>
+          <t>4,07; 7,66</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,72; 8,75</t>
+          <t>4,73; 8,5</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,09; 7,89</t>
+          <t>4,05; 7,53</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,63; 6,77</t>
+          <t>5,19; 7,86</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,15; 7,68</t>
+          <t>1,78; 7,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,79; 12,91</t>
+          <t>5,76; 13,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,53; 9,04</t>
+          <t>3,78; 9,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,42; 10,24</t>
+          <t>5,17; 9,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,82; 13,94</t>
+          <t>7,21; 14,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,62; 17,92</t>
+          <t>10,69; 17,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,24; 14,26</t>
+          <t>7,04; 14,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,18; 14,76</t>
+          <t>10,1; 14,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,9; 11,0</t>
+          <t>5,7; 10,58</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,4; 14,56</t>
+          <t>9,69; 14,85</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,38; 11,2</t>
+          <t>6,36; 11,15</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,8; 12,13</t>
+          <t>8,75; 12,11</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,48; 8,4</t>
+          <t>6,57; 8,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,45; 9,35</t>
+          <t>7,41; 9,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,14; 6,73</t>
+          <t>5,05; 6,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,44; 6,84</t>
+          <t>5,39; 7,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,5; 6,05</t>
+          <t>4,49; 6,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,47; 8,28</t>
+          <t>6,34; 8,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,2</t>
+          <t>4,67; 6,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,72; 6,61</t>
+          <t>5,56; 6,99</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,74; 7,01</t>
+          <t>5,66; 6,94</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7,08; 8,47</t>
+          <t>7,15; 8,54</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5,12; 6,2</t>
+          <t>5,1; 6,21</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,95; 6,47</t>
+          <t>5,71; 6,88</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19137</t>
+          <t>20697</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19928</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39065</t>
+          <t>43289</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>40959; 69347</t>
+          <t>40030; 68270</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>46444; 75220</t>
+          <t>46248; 74574</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31832; 58065</t>
+          <t>31823; 58274</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8259; 39710</t>
+          <t>10072; 41033</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14753; 33030</t>
+          <t>14607; 32598</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21698; 43671</t>
+          <t>21701; 43462</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11402; 27684</t>
+          <t>11366; 27591</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10076; 35485</t>
+          <t>11061; 40375</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>60314; 95123</t>
+          <t>60692; 92954</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74775; 108498</t>
+          <t>73559; 108659</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47899; 78387</t>
+          <t>47348; 78988</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23757; 62839</t>
+          <t>25448; 66494</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27267</t>
+          <t>33196</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14974</t>
+          <t>15337</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>42240</t>
+          <t>48533</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49721; 80856</t>
+          <t>50069; 80501</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65461; 100658</t>
+          <t>66851; 100936</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38651; 66531</t>
+          <t>38486; 63988</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16354; 42442</t>
+          <t>20172; 54007</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24721; 48910</t>
+          <t>25116; 49526</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29075; 53470</t>
+          <t>27880; 53719</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15194; 32888</t>
+          <t>14975; 33708</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7392; 24721</t>
+          <t>8514; 24308</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>81466; 120713</t>
+          <t>79301; 119406</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>101933; 145594</t>
+          <t>100862; 143886</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59466; 91256</t>
+          <t>58335; 90103</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26894; 60733</t>
+          <t>34574; 69424</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37002</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28034</t>
+          <t>30468</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>65037</t>
+          <t>69016</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>33912; 60640</t>
+          <t>33401; 61962</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>42177; 74176</t>
+          <t>42358; 74348</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24680; 49191</t>
+          <t>24788; 49130</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26146; 50917</t>
+          <t>27661; 53850</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12453; 30436</t>
+          <t>12428; 30557</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20186; 41820</t>
+          <t>19925; 40513</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16511; 37975</t>
+          <t>16353; 37165</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20796; 39223</t>
+          <t>21759; 38611</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>51447; 83738</t>
+          <t>51758; 84028</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>69513; 107299</t>
+          <t>66916; 105622</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45981; 79762</t>
+          <t>46037; 78685</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>50208; 80219</t>
+          <t>54885; 85715</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50698</t>
+          <t>55935</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>29385</t>
+          <t>32617</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>80083</t>
+          <t>88552</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30162; 55885</t>
+          <t>29985; 56079</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26618; 51779</t>
+          <t>26569; 51756</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18361; 41487</t>
+          <t>19511; 41747</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21270; 77552</t>
+          <t>41306; 73091</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12237; 31294</t>
+          <t>11698; 30067</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24384; 50008</t>
+          <t>25056; 49211</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15601; 37416</t>
+          <t>15431; 35514</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21295; 38233</t>
+          <t>25347; 42917</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>45633; 78087</t>
+          <t>46910; 79035</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>56420; 93202</t>
+          <t>56947; 92091</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39782; 69104</t>
+          <t>40049; 69499</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45352; 103219</t>
+          <t>71864; 108016</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28933</t>
+          <t>31496</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>35389</t>
+          <t>38304</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>64321</t>
+          <t>69800</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11635; 28606</t>
+          <t>11926; 29167</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7295; 22159</t>
+          <t>6575; 21810</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7736; 22754</t>
+          <t>7382; 23044</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20430; 39795</t>
+          <t>22128; 43763</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>10916; 27833</t>
+          <t>10869; 27584</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29369; 54863</t>
+          <t>29688; 54339</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19783; 42400</t>
+          <t>20721; 45111</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>26954; 45714</t>
+          <t>29993; 48420</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>25886; 50540</t>
+          <t>26589; 49853</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40697; 70469</t>
+          <t>42264; 70188</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31768; 59058</t>
+          <t>32017; 59775</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>50848; 79556</t>
+          <t>57102; 84925</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16285</t>
+          <t>18137</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>32944</t>
+          <t>36209</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>49230</t>
+          <t>54346</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6246; 18045</t>
+          <t>5548; 17820</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10047; 26774</t>
+          <t>10668; 27891</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5584; 18651</t>
+          <t>5530; 18178</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11033; 23757</t>
+          <t>11805; 26095</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17504; 36390</t>
+          <t>17856; 36774</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16596; 35243</t>
+          <t>17452; 36481</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20207; 41001</t>
+          <t>20121; 42588</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13775; 54127</t>
+          <t>28476; 45242</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25715; 47591</t>
+          <t>25891; 48681</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>31319; 58089</t>
+          <t>31412; 56438</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29106; 56152</t>
+          <t>28836; 53640</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>25709; 66138</t>
+          <t>43907; 66488</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20737</t>
+          <t>23013</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>52949</t>
+          <t>56654</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>73686</t>
+          <t>79667</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4512; 16112</t>
+          <t>3727; 16352</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>14463; 32265</t>
+          <t>14396; 33102</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9072; 23244</t>
+          <t>9704; 23388</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15326; 28959</t>
+          <t>16034; 30907</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>22773; 46557</t>
+          <t>24089; 47499</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>41315; 69702</t>
+          <t>41563; 69888</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28991; 57076</t>
+          <t>28157; 58479</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>43360; 62846</t>
+          <t>46905; 67591</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>32069; 59818</t>
+          <t>31003; 57547</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>60035; 93015</t>
+          <t>61898; 94834</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41906; 73584</t>
+          <t>41779; 73244</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>62330; 85939</t>
+          <t>67816; 93835</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>200059</t>
+          <t>221023</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>213603</t>
+          <t>232180</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>413662</t>
+          <t>453203</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>212290; 275280</t>
+          <t>215378; 275818</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>255444; 320308</t>
+          <t>253974; 325624</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>174325; 228532</t>
+          <t>171341; 229041</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>153650; 236555</t>
+          <t>190405; 255818</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>151993; 204526</t>
+          <t>151737; 203313</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>230061; 294681</t>
+          <t>225598; 290532</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>163810; 219660</t>
+          <t>165479; 222649</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>172841; 242043</t>
+          <t>207634; 261005</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>381713; 466311</t>
+          <t>376930; 462125</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>494687; 591726</t>
+          <t>499453; 596415</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>355480; 430098</t>
+          <t>353845; 430711</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>352614; 461129</t>
+          <t>414681; 500325</t>
         </is>
       </c>
     </row>
